--- a/Data_clean/MCAS/Estados_US/Edos_USA_2019/SOUTH_DAKOTA_2019.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2019/SOUTH_DAKOTA_2019.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D174"/>
+  <dimension ref="A1:D168"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Total</t>
@@ -470,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -501,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Arriaga</t>
@@ -514,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>El Porvenir</t>
@@ -527,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Ocotepec</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Total</t>
@@ -584,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Madera</t>
@@ -597,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Namiquipa</t>
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Nuevo Casas Grandes</t>
@@ -623,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Total</t>
@@ -654,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Total</t>
@@ -669,7 +739,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -685,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -698,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -711,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -724,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -737,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -750,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -763,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Total</t>
@@ -794,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -807,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -820,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Total</t>
@@ -835,7 +955,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -851,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Almoloya de Juárez</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C35">
@@ -864,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C36">
@@ -877,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Otzolotepec</t>
@@ -890,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -903,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Tultepec</t>
@@ -916,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Villa Guerrero</t>
@@ -929,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Total</t>
@@ -960,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -973,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>León</t>
@@ -986,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -999,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Santa Cruz de Juventino Rosas</t>
+          <t>Santa Cruz De Juventino Rosas</t>
         </is>
       </c>
       <c r="C46">
@@ -1012,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1032,7 +1212,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C48">
@@ -1043,9 +1223,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ajuchitlán del Progreso</t>
+          <t>Ajuchitlán Del Progreso</t>
         </is>
       </c>
       <c r="C49">
@@ -1056,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C50">
@@ -1069,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C51">
@@ -1082,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C52">
@@ -1095,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Cuajinicuilapa</t>
@@ -1108,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Florencio Villarreal</t>
@@ -1121,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C55">
@@ -1134,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -1147,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Metlatónoc</t>
@@ -1160,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Petatlán</t>
@@ -1173,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C59">
@@ -1186,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Tlapehuala</t>
@@ -1199,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1219,7 +1464,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C62">
@@ -1230,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1261,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Ayutla</t>
@@ -1274,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -1287,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1300,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -1313,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C69">
@@ -1326,9 +1601,14 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>San Diego de Alejandría</t>
+          <t>San Diego De Alejandría</t>
         </is>
       </c>
       <c r="C70">
@@ -1339,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -1352,9 +1637,14 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C72">
@@ -1365,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Tecalitlán</t>
@@ -1378,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Tecolotlán</t>
@@ -1391,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -1404,9 +1709,14 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tlajomulco de Zúñiga</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C76">
@@ -1417,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>San Pedro Tlaquepaque</t>
@@ -1430,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Unión de San Antonio</t>
+          <t>Unión De San Antonio</t>
         </is>
       </c>
       <c r="C78">
@@ -1443,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -1456,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Zapotlanejo</t>
@@ -1469,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1500,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>José Sixto Verduzco</t>
@@ -1513,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Jungapeo</t>
@@ -1526,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -1539,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Purépero</t>
@@ -1552,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -1565,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -1578,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -1591,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -1604,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1635,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -1648,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Tlayacapan</t>
@@ -1661,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -1674,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1705,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Tecuala</t>
@@ -1718,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1749,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1780,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C103">
@@ -1793,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>San José Independencia</t>
@@ -1806,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>San Lorenzo Texmelúcan</t>
@@ -1819,9 +2249,14 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>San Mateo del Mar</t>
+          <t>San Mateo Del Mar</t>
         </is>
       </c>
       <c r="C106">
@@ -1832,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>San Pedro Pochutla</t>
@@ -1845,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>San Pedro Tapanatepec</t>
@@ -1858,9 +2303,14 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Santa Cruz Tacache de Mina</t>
+          <t>Santa Cruz Tacache De Mina</t>
         </is>
       </c>
       <c r="C109">
@@ -1871,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Santa María Temaxcaltepec</t>
@@ -1884,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Santo Domingo Tonalá</t>
@@ -1897,9 +2357,14 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Villa de Tututepec de Melchor Ocampo</t>
+          <t>Villa De Tututepec De Melchor Ocampo</t>
         </is>
       </c>
       <c r="C112">
@@ -1910,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1941,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Jolalpan</t>
@@ -1954,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Tenampulco</t>
@@ -1967,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -1980,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Zacapoaxtla</t>
@@ -1993,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Zacatlán</t>
@@ -2006,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Zaragoza</t>
@@ -2019,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2039,7 +2544,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C122">
@@ -2050,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Pedro Escobedo</t>
@@ -2063,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -2076,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2107,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2138,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Matehuala</t>
@@ -2151,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -2164,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -2177,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2208,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Mazatlán</t>
@@ -2221,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2252,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2283,9 +2843,14 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Jalpa de Méndez</t>
+          <t>Jalpa De Méndez</t>
         </is>
       </c>
       <c r="C139">
@@ -2296,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Tenosique</t>
@@ -2309,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2340,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Altamira</t>
@@ -2353,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>El Mante</t>
@@ -2366,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -2379,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Reynosa</t>
@@ -2392,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Valle Hermoso</t>
@@ -2405,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -2418,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2449,9 +3059,14 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C151">
@@ -2462,9 +3077,14 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ixhuatlán del Café</t>
+          <t>Ixhuatlán Del Café</t>
         </is>
       </c>
       <c r="C152">
@@ -2475,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -2488,9 +3113,14 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C154">
@@ -2501,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Naolinco</t>
@@ -2514,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Naranjos Amatlán</t>
@@ -2527,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -2540,9 +3185,14 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Soledad de Doblado</t>
+          <t>Soledad De Doblado</t>
         </is>
       </c>
       <c r="C158">
@@ -2553,6 +3203,11 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -2566,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Tlapacoyan</t>
@@ -2579,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2610,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Genaro Codina</t>
@@ -2623,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>General Pánfilo Natera</t>
@@ -2636,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Juan Aldama</t>
@@ -2649,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -2662,6 +3347,11 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2685,41 +3375,6 @@
       </c>
       <c r="D168">
         <v>1</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 800,811</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Abril de 2020</t>
-        </is>
       </c>
     </row>
   </sheetData>
